--- a/(枠)◯年度一式/家電受付・実績.xlsx
+++ b/(枠)◯年度一式/家電受付・実績.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr updateLinks="always" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\Desktop\R８年度一式\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB6A6CB-E058-4C29-A33E-CD8FB61A1DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFD3A66-39AF-4B87-B279-74E5A46A259E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="405" windowWidth="18270" windowHeight="14835" tabRatio="695" activeTab="6" xr2:uid="{4B28D2F8-46AC-41C4-96D6-D062E3D8ACA1}"/>
+    <workbookView xWindow="390" yWindow="0" windowWidth="20010" windowHeight="15480" tabRatio="695" activeTab="6" xr2:uid="{4B28D2F8-46AC-41C4-96D6-D062E3D8ACA1}"/>
   </bookViews>
   <sheets>
     <sheet name="発送済Ａ" sheetId="5" r:id="rId1"/>
@@ -1002,16 +1002,38 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Sheet1"/>
+      <sheetName val="A-1"/>
+      <sheetName val="A-2"/>
+      <sheetName val="B-1"/>
+      <sheetName val="収集（全般）"/>
+      <sheetName val="可燃"/>
+      <sheetName val="不燃・木くず・海岸清掃"/>
+      <sheetName val="ビン類"/>
+      <sheetName val="缶類"/>
+      <sheetName val="ペットボトル"/>
+      <sheetName val="紙類"/>
+      <sheetName val="粗大"/>
+      <sheetName val="産廃水産・医療・汚泥"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2">
-            <v>2026</v>
+        <row r="9">
+          <cell r="E9">
+            <v>2027</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1327,8 +1349,8 @@
   <sheetData>
     <row r="1" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="76" t="str">
-        <f>[1]Sheet1!$B$2&amp;"年度家電リサイクル一覧表　（Ａグループ）　　※発送済み"</f>
-        <v>2026年度家電リサイクル一覧表　（Ａグループ）　　※発送済み</v>
+        <f>'[1]A-1'!$E$9&amp;"年度家電リサイクル一覧表　（Ａグループ）　　※発送済み"</f>
+        <v>2027年度家電リサイクル一覧表　（Ａグループ）　　※発送済み</v>
       </c>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -17605,8 +17627,8 @@
   <sheetData>
     <row r="1" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="76" t="str">
-        <f>[1]Sheet1!$B$2&amp;"年度家電リサイクル一覧表　（Ｂグループ）　　※発送済み"</f>
-        <v>2026年度家電リサイクル一覧表　（Ｂグループ）　　※発送済み</v>
+        <f>'[1]A-1'!$E$9&amp;"年度家電リサイクル一覧表　（Ｂグループ）　　※発送済み"</f>
+        <v>2027年度家電リサイクル一覧表　（Ｂグループ）　　※発送済み</v>
       </c>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -23954,8 +23976,8 @@
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="80" t="str">
-        <f>[1]Sheet1!$B$2&amp;"年度家電リサイクル一覧表　　（Ａグループ）"</f>
-        <v>2026年度家電リサイクル一覧表　　（Ａグループ）</v>
+        <f>'[1]A-1'!$E$9&amp;"年度家電リサイクル一覧表　　（Ａグループ）"</f>
+        <v>2027年度家電リサイクル一覧表　　（Ａグループ）</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -27745,8 +27767,8 @@
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="80" t="str">
-        <f>[1]Sheet1!$B$2&amp;"年度家電リサイクル一覧表　　（Ｂグループ）"</f>
-        <v>2026年度家電リサイクル一覧表　　（Ｂグループ）</v>
+        <f>'[1]A-1'!$E$9&amp;"年度家電リサイクル一覧表　　（Ｂグループ）"</f>
+        <v>2027年度家電リサイクル一覧表　　（Ｂグループ）</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -31083,8 +31105,8 @@
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="80" t="str">
-        <f>[1]Sheet1!$B$2&amp;"年度家電リサイクル一覧表　　（Ａグループ）"</f>
-        <v>2026年度家電リサイクル一覧表　　（Ａグループ）</v>
+        <f>'[1]A-1'!$E$9&amp;"年度家電リサイクル一覧表　　（Ａグループ）"</f>
+        <v>2027年度家電リサイクル一覧表　　（Ａグループ）</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -35091,8 +35113,8 @@
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="80" t="str">
-        <f>[1]Sheet1!$B$2&amp;"年度家電リサイクル一覧表　　（Ｂグループ）"</f>
-        <v>2026年度家電リサイクル一覧表　　（Ｂグループ）</v>
+        <f>'[1]A-1'!$E$9&amp;"年度家電リサイクル一覧表　　（Ｂグループ）"</f>
+        <v>2027年度家電リサイクル一覧表　　（Ｂグループ）</v>
       </c>
       <c r="B1" s="80"/>
       <c r="C1" s="80"/>
@@ -38535,8 +38557,8 @@
   <sheetData>
     <row r="1" spans="1:22" s="55" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="85" t="str">
-        <f>[1]Sheet1!$B$2&amp;"年度　家電リサイクル実績表"</f>
-        <v>2026年度　家電リサイクル実績表</v>
+        <f>'[1]A-1'!$E$9&amp;"年度　家電リサイクル実績表"</f>
+        <v>2027年度　家電リサイクル実績表</v>
       </c>
       <c r="B1" s="85"/>
       <c r="C1" s="85"/>
